--- a/notebooks/simulation_results/summary_results_unlabel.xlsx
+++ b/notebooks/simulation_results/summary_results_unlabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/jfj36_bath_ac_uk/Documents/00_Bath_Master/03_Dissertation/src/Goal1/setred/notebooks/simulation_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2B59D2BFD340D34B83CBF4715925A8F76705EA91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC0A80CE-B582-CD49-ABAD-34DFDD9CBF2C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD340D34B83CBF4715925A8F76705EA91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E6A33E-7991-E54F-B407-F8D25E916C75}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="5400" windowWidth="23600" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2600" yWindow="1700" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,6 +144,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,6 +437,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
